--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
@@ -1123,10 +1123,10 @@
         <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>6.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I10" t="n">
         <v>2.16</v>
@@ -2904,7 +2904,7 @@
         <v>2.66</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3152,10 +3152,10 @@
         <v>7.6</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K11" t="n">
         <v>5.6</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
         <v>1.63</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
         <v>2.28</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
@@ -866,7 +866,7 @@
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>990</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="n">
         <v>1.09</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -905,7 +905,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>870</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
         <v>500</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>4.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I9" t="n">
         <v>2.14</v>
@@ -2650,7 +2650,7 @@
         <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>4.9</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.99</v>
       </c>
       <c r="G14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
         <v>4.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Indonesian Super League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>05:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PFK Turan Tovuz</t>
+          <t>Arema Cronus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Sabah</t>
+          <t>Psim Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.74</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>990</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,34 +881,34 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1022,72 +1022,72 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Indonesian Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Dewa United FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Bali Utd Pusam</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.86</v>
+        <v>1.48</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>1.76</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>2.34</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>1.38</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,30 +1351,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>PFK Turan Tovuz</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="G4" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J4" t="n">
         <v>1.01</v>
@@ -1383,219 +1383,219 @@
         <v>500</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FK Sumqayit</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qarabag FK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="G5" t="n">
-        <v>600</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>3.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="K5" t="n">
         <v>500</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.17</v>
+        <v>3.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>660</v>
+        <v>870</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1915,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1927,112 +1927,112 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,72 +2113,72 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FK Sumqayit</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Qarabag FK</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>500</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2289,75 +2289,75 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,37 +2372,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nk Posusje</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>460</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -2435,112 +2435,112 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,37 +2626,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Nk Posusje</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2689,112 +2689,112 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,42 +2875,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2</v>
+        <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>2.66</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2943,112 +2943,112 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,42 +3129,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>9.6</v>
+        <v>990</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>500</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3185,10 +3185,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -3197,112 +3197,112 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -4145,17 +4145,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4658,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4890,7 +4890,515 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,145 +857,145 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
         <v>2.78</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
         <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
         <v>1.01</v>
@@ -1004,7 +1004,7 @@
         <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
         <v>1.01</v>
@@ -1013,61 +1013,61 @@
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
         <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM2" t="n">
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS2" t="n">
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW2" t="n">
         <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY2" t="n">
         <v>1.01</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Indonesian Super League</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dewa United FC</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bali Utd Pusam</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.48</v>
+        <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>1.76</v>
+        <v>2.98</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK3" t="n">
         <v>100</v>
       </c>
-      <c r="J3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Indonesian Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PFK Turan Tovuz</t>
+          <t>Dewa United FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Sabah</t>
+          <t>Bali Utd Pusam</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.74</v>
+        <v>1.54</v>
       </c>
       <c r="G4" t="n">
-        <v>990</v>
+        <v>1.78</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>990</v>
+        <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,33 +1605,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>600</v>
       </c>
       <c r="H5" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7</v>
+        <v>870</v>
       </c>
       <c r="J5" t="n">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>500</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>PFK Turan Tovuz</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="G6" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>870</v>
+        <v>2.24</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
         <v>500</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Sumqayit</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qarabag FK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="G7" t="n">
-        <v>990</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
-        <v>990</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>4.5</v>
+        <v>600</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>2.18</v>
+        <v>870</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nk Posusje</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J9" t="n">
         <v>1.01</v>
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2689,112 +2689,112 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FK Sumqayit</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Qarabag FK</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2898,37 +2898,37 @@
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K10" t="n">
         <v>500</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3051,75 +3051,75 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,37 +3134,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>990</v>
+        <v>2.16</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>500</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3185,10 +3185,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -3197,112 +3197,112 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,42 +3383,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Nk Posusje</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>2.44</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>500</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -3451,112 +3451,112 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,42 +3637,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1.53</v>
+        <v>990</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>500</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3693,10 +3693,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -3705,112 +3705,112 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,42 +3891,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3959,112 +3959,112 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>4.7</v>
       </c>
       <c r="G16" t="n">
-        <v>2.34</v>
+        <v>8.4</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>1.87</v>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>2.04</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4907,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>
@@ -5161,17 +5161,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5398,7 +5398,1023 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 07:02:00</t>
+          <t>2026-05-20 09:17:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SSD Bari</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:17:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:17:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>KR Reykjavik</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:17:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:17:05</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.6</v>
@@ -896,16 +896,16 @@
         <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
         <v>1.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>2.98</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="K3" t="n">
         <v>95</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
         <v>1.01</v>
@@ -1144,22 +1144,22 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
         <v>1.5</v>
@@ -1168,25 +1168,25 @@
         <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA3" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>55</v>
       </c>
       <c r="AI3" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AJ3" t="n">
         <v>85</v>
@@ -1210,16 +1210,16 @@
         <v>220</v>
       </c>
       <c r="AM3" t="n">
-        <v>760</v>
+        <v>730</v>
       </c>
       <c r="AN3" t="n">
         <v>170</v>
       </c>
       <c r="AO3" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.5</v>
@@ -1231,7 +1231,7 @@
         <v>38</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU3" t="n">
         <v>5.7</v>
@@ -1240,34 +1240,34 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC3" t="n">
         <v>24</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
         <v>23</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>21</v>
       </c>
       <c r="BG3" t="n">
         <v>32</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G4" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="H4" t="n">
         <v>5.2</v>
@@ -1377,218 +1377,218 @@
         <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
         <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -1622,227 +1622,227 @@
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>500</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
         <v>1.25</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Croatian HNL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Slaven Belupo</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="G7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H7" t="n">
         <v>3.4</v>
       </c>
-      <c r="H7" t="n">
-        <v>3.05</v>
-      </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.36</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,246 +2372,246 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="G8" t="n">
-        <v>600</v>
+        <v>3.25</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I8" t="n">
-        <v>870</v>
+        <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>2.36</v>
       </c>
       <c r="K8" t="n">
-        <v>500</v>
+        <v>3.15</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2647,225 +2647,225 @@
         <v>870</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>500</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FK Sumqayit</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabag FK</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>990</v>
+        <v>870</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
         <v>500</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FK Sumqayit</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Qarabag FK</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>990</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>2.16</v>
+        <v>990</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>500</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>1.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.17</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,37 +3388,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nk Posusje</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -3451,112 +3451,112 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -3642,25 +3642,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Nk Posusje</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
         <v>1.02</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3914,7 +3914,7 @@
         <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J14" t="n">
         <v>1.02</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,24 +4145,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H15" t="n">
         <v>1.04</v>
@@ -4171,16 +4171,16 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4213,112 +4213,112 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Croatian HNL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Vukovar</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>1.23</v>
       </c>
       <c r="G16" t="n">
-        <v>8.4</v>
+        <v>1.28</v>
       </c>
       <c r="H16" t="n">
-        <v>1.87</v>
+        <v>14.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.04</v>
+        <v>19.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2.98</v>
+        <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,31 +4658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>1.48</v>
+        <v>600</v>
       </c>
       <c r="H17" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>8.800000000000001</v>
+        <v>870</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>500</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,31 +5420,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -5669,17 +5669,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,244 +5923,244 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6414,7 +6414,515 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>KR Reykjavik</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:32:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB66"/>
+  <dimension ref="A1:CB69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
         <v>6.2</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
@@ -899,7 +899,7 @@
         <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
         <v>2.32</v>
@@ -971,10 +971,10 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
         <v>9.4</v>
@@ -986,7 +986,7 @@
         <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
         <v>9</v>
@@ -998,7 +998,7 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
         <v>11.5</v>
@@ -1010,13 +1010,13 @@
         <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>4.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
@@ -1150,19 +1150,19 @@
         <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
         <v>24</v>
@@ -1228,7 +1228,7 @@
         <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1240,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
         <v>14</v>
@@ -1252,19 +1252,19 @@
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.98</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -1392,7 +1392,7 @@
         <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
@@ -1413,10 +1413,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
         <v>11</v>
@@ -1473,7 +1473,7 @@
         <v>210</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>5.5</v>
@@ -1506,7 +1506,7 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
         <v>32</v>
@@ -1515,16 +1515,16 @@
         <v>27</v>
       </c>
       <c r="BD4" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>27</v>
       </c>
       <c r="BG4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
         <v>1.89</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>500</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.34</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
         <v>4.4</v>
@@ -3179,7 +3179,7 @@
         <v>1.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
         <v>2.7</v>
@@ -3194,34 +3194,34 @@
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
         <v>36</v>
       </c>
       <c r="AA11" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
         <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
@@ -3233,7 +3233,7 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK11" t="n">
         <v>23</v>
@@ -3242,19 +3242,19 @@
         <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP11" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
         <v>1.01</v>
@@ -3266,7 +3266,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
         <v>12.5</v>
@@ -3287,7 +3287,7 @@
         <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>15</v>
@@ -3299,7 +3299,7 @@
         <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
         <v>1.24</v>
@@ -3944,7 +3944,7 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4183,13 +4183,13 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
         <v>1.19</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H18" t="n">
         <v>2.4</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.62</v>
-      </c>
       <c r="I18" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4948,7 +4948,7 @@
         <v>2.72</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
         <v>1.66</v>
@@ -4957,46 +4957,46 @@
         <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U18" t="n">
         <v>1.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="W18" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC18" t="n">
         <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF18" t="n">
         <v>22</v>
@@ -5011,49 +5011,49 @@
         <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK18" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
         <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AO18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU18" t="n">
         <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AX18" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AY18" t="n">
         <v>11</v>
@@ -5062,25 +5062,25 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
       </c>
       <c r="BD18" t="n">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF18" t="n">
         <v>23</v>
       </c>
       <c r="BG18" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5175,61 +5175,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="G19" t="n">
         <v>1.35</v>
       </c>
       <c r="H19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J19" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
         <v>2.24</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
         <v>3.9</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>34</v>
@@ -5247,7 +5247,7 @@
         <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
@@ -5259,7 +5259,7 @@
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AI19" t="n">
         <v>230</v>
@@ -5271,13 +5271,13 @@
         <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
@@ -5295,7 +5295,7 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AU19" t="n">
         <v>10.5</v>
@@ -5319,7 +5319,7 @@
         <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC19" t="n">
         <v>11</v>
@@ -5331,7 +5331,7 @@
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -6227,7 +6227,7 @@
         <v>1.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
         <v>3.25</v>
@@ -6356,7 +6356,7 @@
         <v>3.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>3.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
@@ -7880,7 +7880,7 @@
         <v>3.55</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="BJ29" t="n">
         <v>11.5</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7993,13 +7993,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O30" t="n">
         <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q30" t="n">
         <v>1.25</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
         <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8755,13 +8755,13 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="O33" t="n">
         <v>1.23</v>
       </c>
       <c r="P33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q33" t="n">
         <v>1.23</v>
@@ -8770,7 +8770,7 @@
         <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T33" t="n">
         <v>1.11</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9009,13 +9009,13 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O34" t="n">
         <v>1.19</v>
       </c>
       <c r="P34" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q34" t="n">
         <v>1.19</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9484,67 +9484,67 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Brabrand</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Skive</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="G36" t="n">
-        <v>3.15</v>
+        <v>1.22</v>
       </c>
       <c r="H36" t="n">
-        <v>2.64</v>
+        <v>3.35</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="K36" t="n">
-        <v>3.8</v>
+        <v>560</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="T36" t="n">
         <v>1.11</v>
       </c>
-      <c r="N36" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.68</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -9658,55 +9658,55 @@
         <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ36" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BN36" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BP36" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BR36" t="n">
         <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BT36" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BV36" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9738,67 +9738,67 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Brabrand</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HIK Hellerup</t>
+          <t>Skive</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.15</v>
+        <v>2.68</v>
       </c>
       <c r="G37" t="n">
-        <v>1.22</v>
+        <v>3.15</v>
       </c>
       <c r="H37" t="n">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="K37" t="n">
-        <v>560</v>
+        <v>3.75</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="O37" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="P37" t="n">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="R37" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>1.66</v>
+        <v>3.7</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9912,55 +9912,55 @@
         <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BJ37" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BN37" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BP37" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BT37" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BV37" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BZ37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10025,19 +10025,19 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
         <v>1.37</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
         <v>1.36</v>
       </c>
       <c r="R38" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S38" t="n">
         <v>1.37</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
         <v>3.75</v>
       </c>
       <c r="L39" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
         <v>1.09</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="G41" t="n">
         <v>1.63</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
         <v>2.18</v>
       </c>
       <c r="H44" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
         <v>4.4</v>
@@ -11540,10 +11540,10 @@
         <v>3.35</v>
       </c>
       <c r="K44" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L44" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
@@ -11591,7 +11591,7 @@
         <v>110</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC44" t="n">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>150</v>
       </c>
       <c r="AN44" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO44" t="n">
         <v>80</v>
@@ -11639,10 +11639,10 @@
         <v>11</v>
       </c>
       <c r="AR44" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
         <v>7.2</v>
@@ -11651,40 +11651,40 @@
         <v>7.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="n">
         <v>3.15</v>
@@ -11708,7 +11708,7 @@
         <v>4.7</v>
       </c>
       <c r="BO44" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BP44" t="n">
         <v>17.5</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -12042,13 +12042,13 @@
         <v>1.79</v>
       </c>
       <c r="I46" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J46" t="n">
         <v>3.2</v>
       </c>
       <c r="K46" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -12510,14 +12510,14 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12532,246 +12532,246 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="G48" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="H48" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="I48" t="n">
-        <v>2.68</v>
+        <v>2.26</v>
       </c>
       <c r="J48" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K48" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P48" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T48" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X48" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y48" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA48" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ48" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR48" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS48" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT48" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU48" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV48" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW48" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX48" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY48" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ48" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA48" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BB48" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BC48" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD48" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE48" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF48" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG48" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12786,239 +12786,239 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="G49" t="n">
-        <v>1.42</v>
+        <v>2.84</v>
       </c>
       <c r="H49" t="n">
-        <v>9.199999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="I49" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV49" t="n">
         <v>11</v>
       </c>
-      <c r="J49" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AW49" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ49" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -13040,139 +13040,139 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.98</v>
+        <v>1.36</v>
       </c>
       <c r="G50" t="n">
-        <v>3.4</v>
+        <v>1.42</v>
       </c>
       <c r="H50" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I50" t="n">
+        <v>11</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N50" t="n">
         <v>2.34</v>
       </c>
-      <c r="I50" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="O50" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W50" t="n">
         <v>3.35</v>
       </c>
-      <c r="K50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S50" t="n">
-        <v>4</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X50" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Y50" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="Z50" t="n">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="AA50" t="n">
-        <v>40</v>
+        <v>380</v>
       </c>
       <c r="AB50" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AD50" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="AE50" t="n">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="AF50" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AH50" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AI50" t="n">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AJ50" t="n">
-        <v>60</v>
+        <v>13.5</v>
       </c>
       <c r="AK50" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL50" t="n">
         <v>42</v>
       </c>
-      <c r="AL50" t="n">
-        <v>65</v>
-      </c>
       <c r="AM50" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN50" t="n">
-        <v>50</v>
+        <v>6.4</v>
       </c>
       <c r="AO50" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="AP50" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AQ50" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU50" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AV50" t="n">
         <v>1.01</v>
@@ -13181,22 +13181,22 @@
         <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="AY50" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA50" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD50" t="n">
         <v>1.01</v>
@@ -13205,7 +13205,7 @@
         <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="BG50" t="n">
         <v>1.01</v>
@@ -13217,62 +13217,62 @@
         <v>1.01</v>
       </c>
       <c r="BJ50" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN50" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP50" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT50" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV50" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -13294,139 +13294,139 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="G51" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H51" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="I51" t="n">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="J51" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K51" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N51" t="n">
-        <v>1.88</v>
+        <v>3.05</v>
       </c>
       <c r="O51" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="R51" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="S51" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V51" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="W51" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA51" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM51" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV51" t="n">
         <v>1.01</v>
@@ -13435,16 +13435,16 @@
         <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ51" t="n">
         <v>1.01</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB51" t="n">
         <v>1.01</v>
@@ -13459,7 +13459,7 @@
         <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG51" t="n">
         <v>1.01</v>
@@ -13468,65 +13468,65 @@
         <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BJ51" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BN51" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP51" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BT51" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV51" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BZ51" t="n">
         <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -13548,31 +13548,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="G52" t="n">
-        <v>7.2</v>
+        <v>3.05</v>
       </c>
       <c r="H52" t="n">
-        <v>1.63</v>
+        <v>2.56</v>
       </c>
       <c r="I52" t="n">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="K52" t="n">
-        <v>110</v>
+        <v>4.5</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13581,22 +13581,22 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q52" t="n">
         <v>1.9</v>
       </c>
-      <c r="O52" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1.86</v>
-      </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S52" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -13605,10 +13605,10 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>2.26</v>
+        <v>1.5</v>
       </c>
       <c r="W52" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -13802,28 +13802,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="G53" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="H53" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="J53" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="K53" t="n">
         <v>6.4</v>
@@ -13835,22 +13835,22 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="O53" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P53" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R53" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S53" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T53" t="n">
         <v>1.01</v>
@@ -13859,10 +13859,10 @@
         <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="W53" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -14027,14 +14027,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -14056,31 +14056,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="H54" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="I54" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K54" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14089,22 +14089,22 @@
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="O54" t="n">
         <v>1.31</v>
       </c>
       <c r="P54" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R54" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S54" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="T54" t="n">
         <v>1.01</v>
@@ -14113,10 +14113,10 @@
         <v>1.01</v>
       </c>
       <c r="V54" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="W54" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -14310,31 +14310,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="G55" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="I55" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J55" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K55" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -14343,22 +14343,22 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="O55" t="n">
         <v>1.31</v>
       </c>
       <c r="P55" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R55" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T55" t="n">
         <v>1.01</v>
@@ -14367,10 +14367,10 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W55" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -14564,31 +14564,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="G56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J56" t="n">
         <v>3.05</v>
       </c>
-      <c r="H56" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I56" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K56" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -14597,22 +14597,22 @@
         <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="O56" t="n">
         <v>1.31</v>
       </c>
       <c r="P56" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="R56" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S56" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T56" t="n">
         <v>1.01</v>
@@ -14621,10 +14621,10 @@
         <v>1.01</v>
       </c>
       <c r="V56" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W56" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -14789,14 +14789,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -15326,31 +15326,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="G59" t="n">
-        <v>990</v>
+        <v>4.3</v>
       </c>
       <c r="H59" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="I59" t="n">
-        <v>990</v>
+        <v>2.12</v>
       </c>
       <c r="J59" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="K59" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -15359,34 +15359,34 @@
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O59" t="n">
         <v>1.1</v>
       </c>
-      <c r="O59" t="n">
-        <v>1.2</v>
-      </c>
       <c r="P59" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="R59" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="S59" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U59" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V59" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="W59" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -15558,14 +15558,14 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15580,31 +15580,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15613,22 +15613,22 @@
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="O60" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="P60" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="R60" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S60" t="n">
-        <v>1.07</v>
+        <v>2.02</v>
       </c>
       <c r="T60" t="n">
         <v>1.01</v>
@@ -15637,10 +15637,10 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W60" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -15812,14 +15812,14 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15834,239 +15834,239 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M61" t="n">
         <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O61" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P61" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X61" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ61" t="n">
         <v>1.05</v>
       </c>
-      <c r="P61" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q61" t="n">
+      <c r="BR61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS61" t="n">
         <v>1.05</v>
       </c>
-      <c r="R61" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S61" t="n">
+      <c r="BT61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU61" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW61" t="n">
         <v>1.05</v>
       </c>
-      <c r="T61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW61" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BX61" t="n">
         <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ61" t="n">
         <v>1000</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -16124,19 +16124,19 @@
         <v>1.01</v>
       </c>
       <c r="O62" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P62" t="n">
         <v>1.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="R62" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S62" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="T62" t="n">
         <v>1.01</v>
@@ -16313,21 +16313,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16337,36 +16337,36 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Juan Pablo II College</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Melgar</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -16375,22 +16375,22 @@
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="O63" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="P63" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.96</v>
+        <v>1.05</v>
       </c>
       <c r="R63" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S63" t="n">
-        <v>1.96</v>
+        <v>1.05</v>
       </c>
       <c r="T63" t="n">
         <v>1.01</v>
@@ -16399,10 +16399,10 @@
         <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -16574,14 +16574,14 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16591,36 +16591,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -16629,22 +16629,22 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="O64" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="P64" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.58</v>
+        <v>1.06</v>
       </c>
       <c r="R64" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="S64" t="n">
-        <v>2.58</v>
+        <v>1.06</v>
       </c>
       <c r="T64" t="n">
         <v>1.01</v>
@@ -16653,10 +16653,10 @@
         <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -16767,10 +16767,10 @@
         <v>1.01</v>
       </c>
       <c r="BH64" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
@@ -16828,14 +16828,14 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16845,36 +16845,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de Pedro Ju</t>
+          <t>Juan Pablo II College</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Melgar</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -16883,22 +16883,22 @@
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="O65" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="P65" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="R65" t="n">
         <v>1.18</v>
       </c>
       <c r="S65" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="T65" t="n">
         <v>1.01</v>
@@ -16907,10 +16907,10 @@
         <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -17082,14 +17082,14 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -17099,39 +17099,39 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Club 2 de Mayo de Pedro Ju</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M66" t="n">
         <v>1.01</v>
@@ -17140,203 +17140,965 @@
         <v>1.25</v>
       </c>
       <c r="O66" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB66" t="inlineStr">
+        <is>
+          <t>2026-05-20 21:39:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plaza Colonia</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Club Oriental de La Paz</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K67" t="n">
+        <v>440</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB67" t="inlineStr">
+        <is>
+          <t>2026-05-20 21:39:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O68" t="n">
         <v>1.5</v>
       </c>
-      <c r="P66" t="n">
+      <c r="P68" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Q68" t="n">
         <v>2.56</v>
       </c>
-      <c r="R66" t="n">
+      <c r="R68" t="n">
         <v>1.17</v>
       </c>
-      <c r="S66" t="n">
+      <c r="S68" t="n">
         <v>2.56</v>
       </c>
-      <c r="T66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V66" t="n">
+      <c r="T68" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V68" t="n">
         <v>1.2</v>
       </c>
-      <c r="W66" t="n">
+      <c r="W68" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X68" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB68" t="inlineStr">
+        <is>
+          <t>2026-05-20 21:39:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Racing Club (Uru)</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P69" t="n">
         <v>1.64</v>
       </c>
-      <c r="X66" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC66" t="n">
+      <c r="Q69" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X69" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV69" t="n">
         <v>9</v>
       </c>
-      <c r="AD66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BG66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BH66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB66" t="inlineStr">
-        <is>
-          <t>2026-05-20 19:23:18</t>
+      <c r="AW69" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB69" t="inlineStr">
+        <is>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
@@ -872,7 +872,7 @@
         <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.22</v>
@@ -881,10 +881,10 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
         <v>2.6</v>
@@ -971,10 +971,10 @@
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
         <v>9.4</v>
@@ -986,7 +986,7 @@
         <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX2" t="n">
         <v>9</v>
@@ -998,7 +998,7 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB2" t="n">
         <v>11.5</v>
@@ -1010,13 +1010,13 @@
         <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
         <v>4.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>2.78</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.28</v>
@@ -1150,13 +1150,13 @@
         <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
         <v>1.45</v>
@@ -1225,52 +1225,52 @@
         <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
       </c>
       <c r="AV3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>10</v>
       </c>
-      <c r="AW3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="n">
         <v>4.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1374,10 +1374,10 @@
         <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="K4" t="n">
         <v>95</v>
@@ -1389,16 +1389,16 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
         <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1413,7 +1413,7 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
         <v>1.51</v>
@@ -1428,7 +1428,7 @@
         <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB4" t="n">
         <v>11</v>
@@ -1443,40 +1443,40 @@
         <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AJ4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK4" t="n">
         <v>80</v>
       </c>
-      <c r="AK4" t="n">
-        <v>90</v>
-      </c>
       <c r="AL4" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AM4" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="AN4" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AO4" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR4" t="n">
         <v>13.5</v>
@@ -1506,7 +1506,7 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BB4" t="n">
         <v>32</v>
@@ -1515,10 +1515,10 @@
         <v>27</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BF4" t="n">
         <v>27</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1628,13 +1628,13 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H6" t="n">
         <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="J6" t="n">
         <v>3.9</v>
@@ -1903,10 +1903,10 @@
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
         <v>1.35</v>
@@ -1924,7 +1924,7 @@
         <v>1.16</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1996,7 +1996,7 @@
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
         <v>1.01</v>
@@ -2005,7 +2005,7 @@
         <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2178,7 +2178,7 @@
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -2659,10 +2659,10 @@
         <v>1.17</v>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="P9" t="n">
         <v>1.31</v>
@@ -2680,7 +2680,7 @@
         <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="V9" t="n">
         <v>1.41</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -2901,10 +2901,10 @@
         <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2916,19 +2916,19 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
         <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
         <v>4.4</v>
@@ -3182,19 +3182,19 @@
         <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
         <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
@@ -3203,10 +3203,10 @@
         <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
         <v>13.5</v>
@@ -3215,10 +3215,10 @@
         <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
         <v>16.5</v>
@@ -3227,16 +3227,16 @@
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>36</v>
@@ -3245,10 +3245,10 @@
         <v>85</v>
       </c>
       <c r="AN11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
         <v>14.5</v>
@@ -3257,7 +3257,7 @@
         <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
         <v>1.01</v>
@@ -3269,16 +3269,16 @@
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
         <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>12.5</v>
@@ -3287,19 +3287,19 @@
         <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC11" t="n">
         <v>15</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
         <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
         <v>1.86</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4691,10 +4691,10 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>1.87</v>
@@ -4781,10 +4781,10 @@
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
         <v>7.2</v>
@@ -4796,7 +4796,7 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
         <v>10</v>
@@ -4808,7 +4808,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
         <v>19</v>
@@ -4817,16 +4817,16 @@
         <v>17</v>
       </c>
       <c r="BD17" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
         <v>12</v>
       </c>
       <c r="BG17" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
         <v>3.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
         <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4945,7 +4945,7 @@
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="O18" t="n">
         <v>1.38</v>
@@ -4957,7 +4957,7 @@
         <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
         <v>3.5</v>
@@ -4969,7 +4969,7 @@
         <v>1.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W18" t="n">
         <v>1.43</v>
@@ -4984,7 +4984,7 @@
         <v>19.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AB18" t="n">
         <v>12.5</v>
@@ -5017,7 +5017,7 @@
         <v>60</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
         <v>160</v>
@@ -5041,7 +5041,7 @@
         <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU18" t="n">
         <v>6.8</v>
@@ -5053,7 +5053,7 @@
         <v>22</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
         <v>11</v>
@@ -5062,19 +5062,19 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
         <v>23</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G19" t="n">
         <v>1.35</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J19" t="n">
         <v>5.5</v>
       </c>
       <c r="K19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5205,7 +5205,7 @@
         <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
         <v>1.85</v>
@@ -5217,7 +5217,7 @@
         <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
         <v>1.64</v>
@@ -5232,16 +5232,16 @@
         <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z19" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC19" t="n">
         <v>970</v>
@@ -5250,31 +5250,31 @@
         <v>46</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF19" t="n">
         <v>7.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI19" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ19" t="n">
         <v>970</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AN19" t="n">
         <v>7.6</v>
@@ -5286,13 +5286,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>5.9</v>
@@ -5301,40 +5301,40 @@
         <v>10.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AY19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA19" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
         <v>9.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
         <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>85</v>
@@ -5537,7 +5537,7 @@
         <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.01</v>
@@ -5567,7 +5567,7 @@
         <v>7.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.05</v>
+        <v>1.92</v>
       </c>
       <c r="G21" t="n">
         <v>1.93</v>
@@ -5731,7 +5731,7 @@
         <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
         <v>2.06</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
         <v>3.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
         <v>3.55</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ29" t="n">
         <v>11.5</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7996,13 +7996,13 @@
         <v>1.32</v>
       </c>
       <c r="O30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P30" t="n">
         <v>1.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -8250,19 +8250,19 @@
         <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q32" t="n">
         <v>1.5</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.46</v>
       </c>
       <c r="G35" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H35" t="n">
         <v>7.8</v>
@@ -9263,10 +9263,10 @@
         <v>1.04</v>
       </c>
       <c r="N35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P35" t="n">
         <v>2.44</v>
@@ -9293,7 +9293,7 @@
         <v>3</v>
       </c>
       <c r="X35" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
         <v>36</v>
@@ -9308,7 +9308,7 @@
         <v>12</v>
       </c>
       <c r="AC35" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD35" t="n">
         <v>34</v>
@@ -9347,16 +9347,16 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>19</v>
+        <v>3.1</v>
       </c>
       <c r="AQ35" t="n">
         <v>24</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AT35" t="n">
         <v>8.800000000000001</v>
@@ -9368,7 +9368,7 @@
         <v>23</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AX35" t="n">
         <v>8.4</v>
@@ -9377,28 +9377,28 @@
         <v>8.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="BA35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BB35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BD35" t="n">
         <v>24</v>
       </c>
       <c r="BE35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BF35" t="n">
         <v>4.7</v>
       </c>
       <c r="BG35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
         <v>3.75</v>
       </c>
       <c r="L37" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
         <v>1.11</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -10025,13 +10025,13 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O38" t="n">
         <v>1.37</v>
       </c>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q38" t="n">
         <v>1.36</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
         <v>3.75</v>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M39" t="n">
         <v>1.09</v>
@@ -10303,10 +10303,10 @@
         <v>1.87</v>
       </c>
       <c r="V39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>970</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
         <v>2.02</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -11525,25 +11525,25 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="J44" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K44" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L44" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
@@ -11555,7 +11555,7 @@
         <v>1.4</v>
       </c>
       <c r="P44" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q44" t="n">
         <v>2.28</v>
@@ -11564,7 +11564,7 @@
         <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T44" t="n">
         <v>1.81</v>
@@ -11573,19 +11573,19 @@
         <v>1.95</v>
       </c>
       <c r="V44" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W44" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="X44" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y44" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z44" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AA44" t="n">
         <v>110</v>
@@ -11594,10 +11594,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC44" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD44" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE44" t="n">
         <v>65</v>
@@ -11609,10 +11609,10 @@
         <v>11</v>
       </c>
       <c r="AH44" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI44" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ44" t="n">
         <v>25</v>
@@ -11627,10 +11627,10 @@
         <v>150</v>
       </c>
       <c r="AN44" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AO44" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="n">
         <v>9</v>
@@ -11648,7 +11648,7 @@
         <v>7.2</v>
       </c>
       <c r="AU44" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV44" t="n">
         <v>1.01</v>
@@ -11657,7 +11657,7 @@
         <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
         <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="I47" t="n">
         <v>1.57</v>
@@ -12302,7 +12302,7 @@
         <v>4.8</v>
       </c>
       <c r="K47" t="n">
-        <v>110</v>
+        <v>12.5</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
         <v>25</v>
       </c>
       <c r="AF49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG49" t="n">
         <v>12.5</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>1.36</v>
       </c>
       <c r="G50" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H50" t="n">
         <v>9.199999999999999</v>
@@ -13070,16 +13070,16 @@
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O50" t="n">
         <v>1.21</v>
       </c>
       <c r="P50" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q50" t="n">
         <v>1.62</v>
@@ -13088,7 +13088,7 @@
         <v>1.21</v>
       </c>
       <c r="S50" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -13100,7 +13100,7 @@
         <v>1.1</v>
       </c>
       <c r="W50" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="X50" t="n">
         <v>24</v>
@@ -13109,19 +13109,19 @@
         <v>38</v>
       </c>
       <c r="Z50" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA50" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AB50" t="n">
         <v>11</v>
       </c>
       <c r="AC50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD50" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE50" t="n">
         <v>170</v>
@@ -13136,16 +13136,16 @@
         <v>30</v>
       </c>
       <c r="AI50" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ50" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK50" t="n">
         <v>17</v>
       </c>
       <c r="AL50" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM50" t="n">
         <v>160</v>
@@ -13154,7 +13154,7 @@
         <v>6.4</v>
       </c>
       <c r="AO50" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP50" t="n">
         <v>17</v>
@@ -13181,7 +13181,7 @@
         <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY50" t="n">
         <v>8</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -13581,19 +13581,19 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O52" t="n">
         <v>1.31</v>
       </c>
       <c r="P52" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="Q52" t="n">
         <v>1.9</v>
       </c>
       <c r="R52" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="S52" t="n">
         <v>3.2</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -13811,22 +13811,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G53" t="n">
         <v>7.2</v>
       </c>
       <c r="H53" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="I53" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>3.85</v>
       </c>
       <c r="K53" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -13847,7 +13847,7 @@
         <v>1.86</v>
       </c>
       <c r="R53" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
         <v>3.1</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -15081,28 +15081,28 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G58" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="H58" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I58" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J58" t="n">
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
       </c>
       <c r="M58" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N58" t="n">
         <v>2.12</v>
@@ -15111,7 +15111,7 @@
         <v>1.24</v>
       </c>
       <c r="P58" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q58" t="n">
         <v>1.72</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -15335,58 +15335,58 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="G59" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H59" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V59" t="n">
         <v>1.9</v>
       </c>
-      <c r="I59" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J59" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K59" t="n">
-        <v>110</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S59" t="n">
-        <v>2</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.89</v>
-      </c>
       <c r="W59" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -15604,7 +15604,7 @@
         <v>3.25</v>
       </c>
       <c r="K60" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15616,7 +15616,7 @@
         <v>2.24</v>
       </c>
       <c r="O60" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P60" t="n">
         <v>2.24</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -15843,22 +15843,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="G61" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="H61" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="I61" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K61" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L61" t="n">
         <v>1.23</v>
@@ -15867,76 +15867,76 @@
         <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="O61" t="n">
         <v>1.16</v>
       </c>
       <c r="P61" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q61" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V61" t="n">
         <v>1.45</v>
       </c>
-      <c r="R61" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.46</v>
-      </c>
       <c r="W61" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="X61" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z61" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA61" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB61" t="n">
         <v>20</v>
       </c>
       <c r="AC61" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD61" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE61" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF61" t="n">
         <v>24</v>
       </c>
       <c r="AG61" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH61" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI61" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ61" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK61" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL61" t="n">
         <v>32</v>
@@ -15945,10 +15945,10 @@
         <v>60</v>
       </c>
       <c r="AN61" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AO61" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AP61" t="n">
         <v>1.01</v>
@@ -16008,65 +16008,65 @@
         <v>1000</v>
       </c>
       <c r="BI61" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="BJ61" t="n">
         <v>1000</v>
       </c>
       <c r="BK61" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="BL61" t="n">
         <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="BN61" t="n">
         <v>1000</v>
       </c>
       <c r="BO61" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BP61" t="n">
         <v>1000</v>
       </c>
       <c r="BQ61" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="BR61" t="n">
         <v>1000</v>
       </c>
       <c r="BS61" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BT61" t="n">
         <v>1000</v>
       </c>
       <c r="BU61" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BV61" t="n">
         <v>1000</v>
       </c>
       <c r="BW61" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="BX61" t="n">
         <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="BZ61" t="n">
         <v>1000</v>
       </c>
       <c r="CA61" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -17367,19 +17367,19 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G67" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="I67" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J67" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="K67" t="n">
         <v>440</v>
@@ -17415,10 +17415,10 @@
         <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -17538,49 +17538,49 @@
         <v>1000</v>
       </c>
       <c r="BK67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BL67" t="n">
         <v>1000</v>
       </c>
       <c r="BM67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BN67" t="n">
         <v>1000</v>
       </c>
       <c r="BO67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BP67" t="n">
         <v>1000</v>
       </c>
       <c r="BQ67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BR67" t="n">
         <v>1000</v>
       </c>
       <c r="BS67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BT67" t="n">
         <v>1000</v>
       </c>
       <c r="BU67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BV67" t="n">
         <v>1000</v>
       </c>
       <c r="BW67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BX67" t="n">
         <v>1000</v>
       </c>
       <c r="BY67" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BZ67" t="n">
         <v>0</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -17621,28 +17621,28 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="G68" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H68" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I68" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J68" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K68" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
       </c>
       <c r="M68" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N68" t="n">
         <v>1.25</v>
@@ -17666,121 +17666,121 @@
         <v>2.16</v>
       </c>
       <c r="U68" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V68" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W68" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X68" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY68" t="n">
         <v>9.6</v>
       </c>
-      <c r="Y68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AZ68" t="n">
-        <v>1.27</v>
+        <v>21</v>
       </c>
       <c r="BA68" t="n">
-        <v>1.27</v>
+        <v>5.3</v>
       </c>
       <c r="BB68" t="n">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="BC68" t="n">
-        <v>1.27</v>
+        <v>4.7</v>
       </c>
       <c r="BD68" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="BE68" t="n">
-        <v>1.27</v>
+        <v>5.4</v>
       </c>
       <c r="BF68" t="n">
-        <v>1.27</v>
+        <v>18</v>
       </c>
       <c r="BG68" t="n">
-        <v>1.27</v>
+        <v>5.4</v>
       </c>
       <c r="BH68" t="n">
         <v>1000</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -17890,7 +17890,7 @@
         <v>3.3</v>
       </c>
       <c r="K69" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L69" t="n">
         <v>1.44</v>
@@ -17902,10 +17902,10 @@
         <v>2.74</v>
       </c>
       <c r="O69" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P69" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q69" t="n">
         <v>2.36</v>
@@ -17917,10 +17917,10 @@
         <v>4.5</v>
       </c>
       <c r="T69" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U69" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V69" t="n">
         <v>1.67</v>
@@ -17929,7 +17929,7 @@
         <v>1.39</v>
       </c>
       <c r="X69" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y69" t="n">
         <v>8.199999999999999</v>
@@ -17953,7 +17953,7 @@
         <v>38</v>
       </c>
       <c r="AF69" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG69" t="n">
         <v>17</v>
@@ -17992,7 +17992,7 @@
         <v>11</v>
       </c>
       <c r="AS69" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT69" t="n">
         <v>7.6</v>
@@ -18001,10 +18001,10 @@
         <v>6.4</v>
       </c>
       <c r="AV69" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW69" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX69" t="n">
         <v>16.5</v>
@@ -18016,25 +18016,25 @@
         <v>18</v>
       </c>
       <c r="BA69" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB69" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC69" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BD69" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BE69" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BF69" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BG69" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH69" t="n">
         <v>1000</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-22 20:41:22</t>
+          <t>2026-05-22 23:15:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,108 +1097,108 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>7.8</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>960</v>
       </c>
       <c r="J3" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.72</v>
+        <v>12.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="M3" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.44</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>1.26</v>
       </c>
       <c r="R3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.02</v>
       </c>
-      <c r="S3" t="n">
-        <v>26</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.14</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>780</v>
+        <v>950</v>
       </c>
       <c r="AC3" t="n">
         <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
@@ -1219,129 +1219,129 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.4</v>
+        <v>1.43</v>
       </c>
       <c r="AR3" t="n">
-        <v>38</v>
+        <v>1.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>1.43</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.05</v>
+        <v>1.43</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.15</v>
+        <v>1.36</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.38</v>
+        <v>1.42</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>1.81</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>1.79</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>50</v>
+        <v>1.59</v>
       </c>
       <c r="BG3" t="n">
-        <v>32</v>
+        <v>1.51</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-22 20:41:22</t>
+          <t>2026-05-22 23:15:43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,88 +1356,88 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>CSD Rangers</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
         <v>5.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="O4" t="n">
-        <v>1.14</v>
+        <v>2.62</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>1.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="S4" t="n">
-        <v>1.54</v>
+        <v>110</v>
       </c>
       <c r="T4" t="n">
-        <v>1.46</v>
+        <v>2.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.71</v>
+        <v>4.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB4" t="n">
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
@@ -1446,7 +1446,7 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1473,129 +1473,129 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.04</v>
+        <v>55</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.04</v>
+        <v>48</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>44</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.02</v>
+        <v>9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.02</v>
+        <v>9</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.04</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-22 20:41:22</t>
+          <t>2026-05-22 23:15:43</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,747 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSD Rangers</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="G5" t="n">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>1.08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.78</v>
+        <v>1.09</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.38</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>46</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>180</v>
+        <v>12</v>
       </c>
       <c r="AN5" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="BA5" t="n">
-        <v>40</v>
+        <v>1.22</v>
       </c>
       <c r="BB5" t="n">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>85</v>
+        <v>4.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
-        <v>21</v>
+        <v>1.09</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-22 20:41:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Independiente (Ecu)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>11</v>
-      </c>
-      <c r="I6" t="n">
-        <v>13</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>230</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>430</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>110</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>960</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-05-22 20:41:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks FC</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Hartford Athletic FC</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>90</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-05-22 20:41:22</t>
+          <t>2026-05-22 23:15:43</t>
         </is>
       </c>
     </row>
